--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,26 +449,26 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ClaimResponse.extension:MealCostExcemption</t>
-  </si>
-  <si>
-    <t>MealCostExcemption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-MealCostExcemption}
+    <t>ClaimResponse.extension:VerpflegskostenBeitragsbefreiung</t>
+  </si>
+  <si>
+    <t>VerpflegskostenBeitragsbefreiung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verpflegskostenBeitragsbefreiung}
 </t>
   </si>
   <si>
     <t>"VKBEFR – Verpflegskosten-Beitragsbefreiung"</t>
   </si>
   <si>
-    <t>ClaimResponse.extension:NumberOfPreviouslyPaidDays</t>
-  </si>
-  <si>
-    <t>NumberOfPreviouslyPaidDays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-NumberOfPreviouslyPaidDays}
+    <t>ClaimResponse.extension:VortageanzahlAufKostenbeitrag</t>
+  </si>
+  <si>
+    <t>VortageanzahlAufKostenbeitrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-vortageanzahlAufKostenbeitrag}
 </t>
   </si>
   <si>
@@ -2755,7 +2755,7 @@
   <cols>
     <col min="1" max="1" width="58.4765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="58.4765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="32.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="48.5859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedVAEResponse</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedVAEResponse</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,19 +54,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -455,7 +455,7 @@
     <t>VerpflegskostenBeitragsbefreiung</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verpflegskostenBeitragsbefreiung}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-verpflegskostenBeitragsbefreiung}
 </t>
   </si>
   <si>
@@ -468,7 +468,7 @@
     <t>VortageanzahlAufKostenbeitrag</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-vortageanzahlAufKostenbeitrag}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-vortageanzahlAufKostenbeitrag}
 </t>
   </si>
   <si>
@@ -902,7 +902,7 @@
     <t>ClaimResponse.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedVAERequest)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedVAERequest)
 </t>
   </si>
   <si>
@@ -954,7 +954,7 @@
     <t>To advise the requestor of the result of the adjudication process.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-VAEStatus-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-VAEStatus-valueset</t>
   </si>
   <si>
     <t>ClaimResponse.disposition</t>
@@ -2337,7 +2337,7 @@
     <t>ClaimResponse.insurance.coverage</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedCoverage)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedCoverage)
 </t>
   </si>
   <si>
@@ -2778,7 +2778,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.6328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.33984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAEResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
